--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R16449c732bd744f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38f850cc235f4a5c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R38f850cc235f4a5c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree3010920e8847e0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ree3010920e8847e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd95670fef4ed479e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rd95670fef4ed479e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2974a000ac1f4d41"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R2974a000ac1f4d41"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d8d0652f557465b"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R3d8d0652f557465b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31175a28d1d74647"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R31175a28d1d74647"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R520f3c378f4744d8"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R520f3c378f4744d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R887b3616fd4e4381"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R887b3616fd4e4381"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99a843be82514e3c"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R99a843be82514e3c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re56a463493514ebf"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re56a463493514ebf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R47fd053d696147d4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R47fd053d696147d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f18b56f265f4528"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R1f18b56f265f4528"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57ec2c400f2140b0"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R57ec2c400f2140b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b8094b5b6924015"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
+++ b/tests/Kookerella.FsOpenXmlDsl.Tests/Examples/ConditionalFormat_CellValueRule/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0b8094b5b6924015"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfcf83d8d37334d17"/>
   </x:sheets>
 </x:workbook>
 </file>
